--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/bio-bio.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6364.48</v>
+        <v>6310.57</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7232.69</v>
+        <v>7258.51</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>776.48</v>
+        <v>774.8</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1213.84</v>
+        <v>1212.13</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2954.99</v>
+        <v>2958.78</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3855.23</v>
+        <v>3896.58</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5492.34</v>
+        <v>5551.25</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4670.93</v>
+        <v>4696.48</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1679.47</v>
+        <v>1688.66</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>635.55</v>
+        <v>635.11</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3177.68</v>
+        <v>3175.51</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8998.5</v>
+        <v>8992.360000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>635.55</v>
+        <v>632.1900000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5084.29</v>
+        <v>5207.92</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>799.17</v>
+        <v>801.37</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>24581.37</v>
+        <v>24678.29</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7692.85</v>
+        <v>7593.81</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12801.81</v>
+        <v>13002.34</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15477.64</v>
+        <v>15117.48</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>684.52</v>
+        <v>692.95</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7118.87</v>
+        <v>7198.49</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2655.54</v>
+        <v>2685.24</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>277.65</v>
+        <v>280.29</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>11446.3</v>
+        <v>11580.57</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1584.67</v>
+        <v>1603.26</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>714.09</v>
+        <v>708.67</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5372.67</v>
+        <v>5293.07</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4353.52</v>
+        <v>4397.31</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1142.79</v>
+        <v>1137.01</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,68 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7190.85</v>
+        <v>7238.98</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1208129-410-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/bio-bio.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1036-301-CM25</t>
+          <t>2408-3831-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6310.57</v>
+        <v>39018.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2408-4721-CM25</t>
+          <t>1426098-91-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7258.51</v>
+        <v>621.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1650-622-CM25</t>
+          <t>4494-552-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.204-0</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hospital Santa Juana</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.292.846-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>774.8</v>
+        <v>4234.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2416-472-CM25</t>
+          <t>1036-301-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1212.13</v>
+        <v>6310.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1650-653-CM25</t>
+          <t>2408-4721-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.602.204-0</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hospital Santa Juana</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2958.78</v>
+        <v>7258.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2771-734-CM25</t>
+          <t>1650-622-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>61.602.204-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>Hospital Santa Juana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3896.58</v>
+        <v>774.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2771-735-CM25</t>
+          <t>2416-472-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5551.25</v>
+        <v>1212.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2785-4508-CM25</t>
+          <t>1650-653-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>61.602.204-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>Hospital Santa Juana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4696.48</v>
+        <v>2958.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2785-4509-CM25</t>
+          <t>2771-734-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1688.66</v>
+        <v>3896.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1969-38-CM26</t>
+          <t>2771-735-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.004.068-3</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>635.11</v>
+        <v>5551.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1036-5-CM26</t>
+          <t>2785-4508-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3175.51</v>
+        <v>4696.48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1036-8-CM26</t>
+          <t>2785-4509-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8992.360000000001</v>
+        <v>1688.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1969-44-CM26</t>
+          <t>1969-38-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>632.1900000000001</v>
+        <v>635.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1036-22-CM26</t>
+          <t>1036-5-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5207.92</v>
+        <v>3175.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4351-54-CM26</t>
+          <t>1036-8-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>801.37</v>
+        <v>8992.360000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2416-16-CM26</t>
+          <t>1969-44-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.004.068-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>Dirección Regional de Gendarmeria - Concepcion</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>24678.29</v>
+        <v>632.1900000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2416-20-CM26</t>
+          <t>1036-22-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7593.81</v>
+        <v>5207.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3945-133-CM26</t>
+          <t>4351-54-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL MODO SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.712.337-K</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>13002.34</v>
+        <v>801.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1063796-7-CM26</t>
+          <t>2416-16-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15117.48</v>
+        <v>24678.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4351-175-CM26</t>
+          <t>2416-20-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>692.95</v>
+        <v>7593.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1426098-120-CM26</t>
+          <t>3945-133-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL MODO SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.712.337-K</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7198.49</v>
+        <v>13002.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1426098-121-CM26</t>
+          <t>1063796-7-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2685.24</v>
+        <v>15117.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1208129-263-CM26</t>
+          <t>4351-175-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>280.29</v>
+        <v>692.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4494-311-CM26</t>
+          <t>1426098-120-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>11580.57</v>
+        <v>7198.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2759-348-CM26</t>
+          <t>1426098-121-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1603.26</v>
+        <v>2685.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057419-260-CM26</t>
+          <t>1208129-263-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.607.304-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL SANTA BARBARA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>708.67</v>
+        <v>280.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4494-423-CM26</t>
+          <t>4494-311-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5293.07</v>
+        <v>11580.57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2785-467-CM26</t>
+          <t>2759-348-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4397.31</v>
+        <v>1603.26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1161266-450-CM26</t>
+          <t>1057419-260-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.141.800-6</t>
+          <t>61.607.304-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL SANTA BARBARA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1137.01</v>
+        <v>708.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3355-254-CM26</t>
+          <t>4494-423-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7238.98</v>
+        <v>5293.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1208129-410-CM26</t>
+          <t>2785-467-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,6 +2399,189 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
+        <v>4397.31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1161266-450-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.141.800-6</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>1137.01</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3355-254-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.101.076-1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>7238.98</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1208129-410-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>204</v>
       </c>
     </row>
